--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>164072.81</v>
+        <v>170379.41</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4816262.43</v>
+        <v>4816789.48</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1783,13 +1783,13 @@
         <v>4422561.28</v>
       </c>
       <c r="P10" t="n">
-        <v>8115296.32</v>
+        <v>8294215.64</v>
       </c>
       <c r="Q10" t="n">
         <v>3096601.89</v>
       </c>
       <c r="R10" t="n">
-        <v>20065682.11</v>
+        <v>20244601.43</v>
       </c>
       <c r="S10" t="n">
         <v>9800225.01</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>9307870.02</v>
+        <v>10570590.51</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>121474.12</v>
+        <v>164249.32</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1145867.82</v>
+        <v>1147094.82</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>9491055.880000001</v>
+        <v>9491342.720000001</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2611298.09</v>
+        <v>2986467.8</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1906526.94</v>
+        <v>1908014.44</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5420,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1906526.94</v>
+        <v>1907530.04</v>
       </c>
       <c r="P36" t="n">
         <v>2931914.44</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>706433.0600000001</v>
+        <v>825646.38</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -13972,10 +13972,10 @@
         <v>150000</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="U97" t="n">
         <v>150000</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -14651,7 +14651,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>9750.41</v>
+        <v>16057.01</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>73500</v>
+        <v>75642</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -18312,10 +18312,10 @@
         <v>150000</v>
       </c>
       <c r="S128" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="T128" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="U128" t="n">
         <v>150000</v>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -22071,7 +22071,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>9099.6</v>
+        <v>15406.2</v>
       </c>
       <c r="M155" t="n">
         <v>0</v>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -23051,7 +23051,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>133731.79</v>
+        <v>134059.79</v>
       </c>
       <c r="M162" t="n">
         <v>0</v>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -23471,7 +23471,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>134010.89</v>
+        <v>147652.91</v>
       </c>
       <c r="M165" t="n">
         <v>0</v>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -24451,7 +24451,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="M172" t="n">
         <v>0</v>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -25431,7 +25431,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>200000</v>
+        <v>350000</v>
       </c>
       <c r="M179" t="n">
         <v>0</v>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -26271,7 +26271,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6289600</v>
+        <v>7122000</v>
       </c>
       <c r="M185" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -26551,7 +26551,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>82853.60000000001</v>
+        <v>89160.2</v>
       </c>
       <c r="M187" t="n">
         <v>0</v>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -26831,7 +26831,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>744555.9399999999</v>
+        <v>774265.55</v>
       </c>
       <c r="M189" t="n">
         <v>0</v>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -29911,7 +29911,7 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>30296477.82</v>
+        <v>34068633.7</v>
       </c>
       <c r="M211" t="n">
         <v>0</v>
@@ -29932,10 +29932,10 @@
         <v>46522205.13</v>
       </c>
       <c r="S211" t="n">
-        <v>45922205.12</v>
+        <v>46522205.12</v>
       </c>
       <c r="T211" t="n">
-        <v>45922205.12</v>
+        <v>46522205.12</v>
       </c>
       <c r="U211" t="n">
         <v>46522205.13</v>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -30471,7 +30471,7 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>135644990.41</v>
+        <v>138273116.26</v>
       </c>
       <c r="M215" t="n">
         <v>0</v>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -31031,7 +31031,7 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>54741982.83</v>
+        <v>54893496.57</v>
       </c>
       <c r="M219" t="n">
         <v>0</v>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>
@@ -32011,7 +32011,7 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>35362303.78</v>
+        <v>36382287.88</v>
       </c>
       <c r="M226" t="n">
         <v>0</v>
@@ -32023,13 +32023,13 @@
         <v>35122742.46</v>
       </c>
       <c r="P226" t="n">
-        <v>6388346.56</v>
+        <v>6884747.48</v>
       </c>
       <c r="Q226" t="n">
         <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>48542457.07</v>
+        <v>49535258.91</v>
       </c>
       <c r="S226" t="n">
         <v>39254641.52</v>
@@ -32038,7 +32038,7 @@
         <v>40867405.68</v>
       </c>
       <c r="U226" t="n">
-        <v>42154110.51</v>
+        <v>42650511.43</v>
       </c>
       <c r="V226" t="n">
         <v>1612764.16</v>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>01/09/2026 11:16:15</t>
+          <t>02/09/2026 10:41:15</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>77609.89</v>
+        <v>78677.89</v>
       </c>
       <c r="P6" t="n">
         <v>24053.29</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         <v>115966</v>
       </c>
       <c r="O8" t="n">
-        <v>117278.61</v>
+        <v>118327.6</v>
       </c>
       <c r="P8" t="n">
         <v>272020.19</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4816789.48</v>
+        <v>4856311.31</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>295928.97</v>
       </c>
       <c r="O10" t="n">
-        <v>4422561.28</v>
+        <v>4742385.19</v>
       </c>
       <c r="P10" t="n">
         <v>8294215.64</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
         <v>197487</v>
       </c>
       <c r="O11" t="n">
-        <v>163440.91</v>
+        <v>163590.91</v>
       </c>
       <c r="P11" t="n">
         <v>200450</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -3180,16 +3180,16 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2962311.1</v>
+        <v>3503838.53</v>
       </c>
       <c r="P20" t="n">
-        <v>4059321.98</v>
+        <v>4312664.33</v>
       </c>
       <c r="Q20" t="n">
-        <v>25486</v>
+        <v>316899.89</v>
       </c>
       <c r="R20" t="n">
-        <v>9775451.98</v>
+        <v>10318646.26</v>
       </c>
       <c r="S20" t="n">
         <v>5436742.02</v>
@@ -3198,13 +3198,13 @@
         <v>5585658.05</v>
       </c>
       <c r="U20" t="n">
-        <v>5716130</v>
+        <v>6005981.93</v>
       </c>
       <c r="V20" t="n">
         <v>148916.03</v>
       </c>
       <c r="W20" t="n">
-        <v>5716130</v>
+        <v>6007543.89</v>
       </c>
       <c r="X20" t="n">
         <v>6766333</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
         <v>1142642.78</v>
       </c>
       <c r="P30" t="n">
-        <v>652919.54</v>
+        <v>653221.75</v>
       </c>
       <c r="Q30" t="n">
         <v>9180</v>
@@ -4592,13 +4592,13 @@
         <v>2600214.6</v>
       </c>
       <c r="S30" t="n">
-        <v>1778615.7</v>
+        <v>1796983.06</v>
       </c>
       <c r="T30" t="n">
-        <v>1935206.48</v>
+        <v>1953573.84</v>
       </c>
       <c r="U30" t="n">
-        <v>1947295.06</v>
+        <v>1946992.85</v>
       </c>
       <c r="V30" t="n">
         <v>156590.78</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
         <v>725144</v>
       </c>
       <c r="O32" t="n">
-        <v>8651702.98</v>
+        <v>9407082.59</v>
       </c>
       <c r="P32" t="n">
         <v>5847047.17</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
         <v>110000</v>
       </c>
       <c r="O33" t="n">
-        <v>412659.85</v>
+        <v>432521.77</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>82538.81</v>
+        <v>98254.77</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -5164,13 +5164,13 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>507458</v>
+        <v>281044.11</v>
       </c>
       <c r="X34" t="n">
         <v>510000</v>
       </c>
       <c r="Y34" t="n">
-        <v>2542</v>
+        <v>228955.89</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1907530.04</v>
+        <v>1907666.15</v>
       </c>
       <c r="P36" t="n">
         <v>2931914.44</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
         <v>131526</v>
       </c>
       <c r="O43" t="n">
-        <v>8828.879999999999</v>
+        <v>9985.280000000001</v>
       </c>
       <c r="P43" t="n">
         <v>98795.48</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -6537,19 +6537,19 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>96992.57000000001</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>187832.03</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -6558,13 +6558,13 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>90839.46000000001</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
@@ -6576,7 +6576,7 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AB44" t="n">
         <v>5</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -6820,16 +6820,16 @@
         <v>93886</v>
       </c>
       <c r="O46" t="n">
-        <v>2499309.9</v>
+        <v>2696862.84</v>
       </c>
       <c r="P46" t="n">
-        <v>16770780.47</v>
+        <v>16894848.03</v>
       </c>
       <c r="Q46" t="n">
         <v>5379029</v>
       </c>
       <c r="R46" t="n">
-        <v>31080819.1</v>
+        <v>31146339.64</v>
       </c>
       <c r="S46" t="n">
         <v>5410326.72</v>
@@ -6838,13 +6838,13 @@
         <v>5910269.36</v>
       </c>
       <c r="U46" t="n">
-        <v>14310038.63</v>
+        <v>14251491.61</v>
       </c>
       <c r="V46" t="n">
         <v>499942.64</v>
       </c>
       <c r="W46" t="n">
-        <v>14470561.05</v>
+        <v>14320561.05</v>
       </c>
       <c r="X46" t="n">
         <v>21072104</v>
@@ -6853,10 +6853,10 @@
         <v>5379029</v>
       </c>
       <c r="Z46" t="n">
-        <v>6695428.95</v>
+        <v>6845428.95</v>
       </c>
       <c r="AA46" t="n">
-        <v>14470561.05</v>
+        <v>14320561.05</v>
       </c>
       <c r="AB46" t="n">
         <v>5</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -14791,7 +14791,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>245768.58</v>
+        <v>276820.97</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -14940,7 +14940,7 @@
         <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>97826.36</v>
+        <v>114042.91</v>
       </c>
       <c r="P104" t="n">
         <v>260024.05</v>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -21684,13 +21684,13 @@
         <v>11000</v>
       </c>
       <c r="W152" t="n">
-        <v>7704296</v>
+        <v>7639296</v>
       </c>
       <c r="X152" t="n">
         <v>8429440</v>
       </c>
       <c r="Y152" t="n">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="Z152" t="n">
         <v>725144</v>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -21940,7 +21940,7 @@
         <v>0</v>
       </c>
       <c r="O154" t="n">
-        <v>39157.62</v>
+        <v>39514.57</v>
       </c>
       <c r="P154" t="n">
         <v>0</v>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -22360,7 +22360,7 @@
         <v>190000</v>
       </c>
       <c r="O157" t="n">
-        <v>202787.33</v>
+        <v>236546.44</v>
       </c>
       <c r="P157" t="n">
         <v>348715.49</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -23191,7 +23191,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>485922.72</v>
+        <v>566909.84</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -23340,7 +23340,7 @@
         <v>211572</v>
       </c>
       <c r="O164" t="n">
-        <v>1554642.66</v>
+        <v>1655046.36</v>
       </c>
       <c r="P164" t="n">
         <v>2681434.52</v>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -23900,7 +23900,7 @@
         <v>308638.89</v>
       </c>
       <c r="O168" t="n">
-        <v>0</v>
+        <v>308638.89</v>
       </c>
       <c r="P168" t="n">
         <v>308630.89</v>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -24040,7 +24040,7 @@
         <v>652646.5600000001</v>
       </c>
       <c r="O169" t="n">
-        <v>0</v>
+        <v>652646.5600000001</v>
       </c>
       <c r="P169" t="n">
         <v>0</v>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -25452,10 +25452,10 @@
         <v>578000</v>
       </c>
       <c r="S179" t="n">
-        <v>350000</v>
+        <v>578000</v>
       </c>
       <c r="T179" t="n">
-        <v>350000</v>
+        <v>578000</v>
       </c>
       <c r="U179" t="n">
         <v>578000</v>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -26980,16 +26980,16 @@
         <v>0</v>
       </c>
       <c r="O190" t="n">
-        <v>1465931.48</v>
+        <v>1520782.37</v>
       </c>
       <c r="P190" t="n">
-        <v>2239845.37</v>
+        <v>2316998.65</v>
       </c>
       <c r="Q190" t="n">
         <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>5565604.28</v>
+        <v>5642757.56</v>
       </c>
       <c r="S190" t="n">
         <v>2403429.22</v>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -28520,7 +28520,7 @@
         <v>0</v>
       </c>
       <c r="O201" t="n">
-        <v>255660.84</v>
+        <v>273660.67</v>
       </c>
       <c r="P201" t="n">
         <v>2957320.94</v>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -30480,7 +30480,7 @@
         <v>0</v>
       </c>
       <c r="O215" t="n">
-        <v>126289723.58</v>
+        <v>126414514.22</v>
       </c>
       <c r="P215" t="n">
         <v>49808521.04</v>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -30900,7 +30900,7 @@
         <v>0</v>
       </c>
       <c r="O218" t="n">
-        <v>67129713.70999999</v>
+        <v>69557963.70999999</v>
       </c>
       <c r="P218" t="n">
         <v>62818272</v>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -31031,7 +31031,7 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>54893496.57</v>
+        <v>55047627.33</v>
       </c>
       <c r="M219" t="n">
         <v>0</v>
@@ -31040,7 +31040,7 @@
         <v>0</v>
       </c>
       <c r="O219" t="n">
-        <v>54317773.95</v>
+        <v>54471982.83</v>
       </c>
       <c r="P219" t="n">
         <v>50438263.91</v>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -31332,7 +31332,7 @@
         <v>1406720</v>
       </c>
       <c r="S221" t="n">
-        <v>1406720</v>
+        <v>1373122.99</v>
       </c>
       <c r="T221" t="n">
         <v>1406720</v>
@@ -31341,7 +31341,7 @@
         <v>1406720</v>
       </c>
       <c r="V221" t="n">
-        <v>0</v>
+        <v>33597.01</v>
       </c>
       <c r="W221" t="n">
         <v>1406720</v>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>02/09/2026 10:41:15</t>
+          <t>03/09/2026 10:43:09</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>78677.89</v>
+        <v>79745.89</v>
       </c>
       <c r="P6" t="n">
         <v>24053.29</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
         <v>4742385.19</v>
       </c>
       <c r="P10" t="n">
-        <v>8294215.64</v>
+        <v>8388914.42</v>
       </c>
       <c r="Q10" t="n">
         <v>3096601.89</v>
@@ -1792,16 +1792,16 @@
         <v>20244601.43</v>
       </c>
       <c r="S10" t="n">
-        <v>9800225.01</v>
+        <v>9705526.23</v>
       </c>
       <c r="T10" t="n">
-        <v>11177480.51</v>
+        <v>11248777.65</v>
       </c>
       <c r="U10" t="n">
-        <v>11950385.79</v>
+        <v>11855687.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1377255.5</v>
+        <v>1543251.42</v>
       </c>
       <c r="W10" t="n">
         <v>11952587.12</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -4863,25 +4863,25 @@
         <v>9407082.59</v>
       </c>
       <c r="P32" t="n">
-        <v>5847047.17</v>
+        <v>6111721.43</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>24425317.39</v>
+        <v>24790341.23</v>
       </c>
       <c r="S32" t="n">
-        <v>17196108.69</v>
+        <v>17430458.27</v>
       </c>
       <c r="T32" t="n">
-        <v>20848457.37</v>
+        <v>21213481.21</v>
       </c>
       <c r="U32" t="n">
-        <v>18578270.22</v>
+        <v>18678619.8</v>
       </c>
       <c r="V32" t="n">
-        <v>3652348.68</v>
+        <v>3783022.94</v>
       </c>
       <c r="W32" t="n">
         <v>18679488</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -6823,25 +6823,25 @@
         <v>2696862.84</v>
       </c>
       <c r="P46" t="n">
-        <v>16894848.03</v>
+        <v>17377529.65</v>
       </c>
       <c r="Q46" t="n">
         <v>5379029</v>
       </c>
       <c r="R46" t="n">
-        <v>31146339.64</v>
+        <v>31629021.26</v>
       </c>
       <c r="S46" t="n">
-        <v>5410326.72</v>
+        <v>5894529.44</v>
       </c>
       <c r="T46" t="n">
-        <v>5910269.36</v>
+        <v>6394979</v>
       </c>
       <c r="U46" t="n">
         <v>14251491.61</v>
       </c>
       <c r="V46" t="n">
-        <v>499942.64</v>
+        <v>500449.56</v>
       </c>
       <c r="W46" t="n">
         <v>14320561.05</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -10737,7 +10737,7 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10764,7 +10764,7 @@
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="X74" t="n">
         <v>0</v>
@@ -10776,7 +10776,7 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="AB74" t="n">
         <v>5</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>200000</v>
+        <v>700000</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -11324,7 +11324,7 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>200000</v>
+        <v>700000</v>
       </c>
       <c r="X78" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>200000</v>
+        <v>700000</v>
       </c>
       <c r="AB78" t="n">
         <v>5</v>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -11997,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>150000</v>
+        <v>450000</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -12012,10 +12012,10 @@
         <v>150000</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="U83" t="n">
         <v>150000</v>
@@ -12024,7 +12024,7 @@
         <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>150000</v>
+        <v>450000</v>
       </c>
       <c r="X83" t="n">
         <v>0</v>
@@ -12036,7 +12036,7 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>150000</v>
+        <v>450000</v>
       </c>
       <c r="AB83" t="n">
         <v>5</v>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -12137,7 +12137,7 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>250000</v>
+        <v>350000</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -12164,7 +12164,7 @@
         <v>0</v>
       </c>
       <c r="W84" t="n">
-        <v>250000</v>
+        <v>350000</v>
       </c>
       <c r="X84" t="n">
         <v>0</v>
@@ -12176,7 +12176,7 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>250000</v>
+        <v>350000</v>
       </c>
       <c r="AB84" t="n">
         <v>5</v>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -12977,7 +12977,7 @@
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>260000</v>
+        <v>366101.6</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13004,7 +13004,7 @@
         <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>260000</v>
+        <v>366101.6</v>
       </c>
       <c r="X90" t="n">
         <v>0</v>
@@ -13016,7 +13016,7 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>260000</v>
+        <v>366101.6</v>
       </c>
       <c r="AB90" t="n">
         <v>5</v>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -13397,7 +13397,7 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -13424,7 +13424,7 @@
         <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="X93" t="n">
         <v>0</v>
@@ -13436,7 +13436,7 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AB93" t="n">
         <v>5</v>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13704,7 +13704,7 @@
         <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="X95" t="n">
         <v>0</v>
@@ -13716,7 +13716,7 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AB95" t="n">
         <v>5</v>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -19417,7 +19417,7 @@
         <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>235000</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -19444,7 +19444,7 @@
         <v>0</v>
       </c>
       <c r="W136" t="n">
-        <v>0</v>
+        <v>235000</v>
       </c>
       <c r="X136" t="n">
         <v>0</v>
@@ -19456,7 +19456,7 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>235000</v>
       </c>
       <c r="AB136" t="n">
         <v>5</v>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -23343,13 +23343,13 @@
         <v>1655046.36</v>
       </c>
       <c r="P164" t="n">
-        <v>2681434.52</v>
+        <v>2709234.52</v>
       </c>
       <c r="Q164" t="n">
         <v>324976</v>
       </c>
       <c r="R164" t="n">
-        <v>6629661.87</v>
+        <v>6657461.87</v>
       </c>
       <c r="S164" t="n">
         <v>2878721.84</v>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -24737,7 +24737,7 @@
         <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -24764,7 +24764,7 @@
         <v>0</v>
       </c>
       <c r="W174" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="X174" t="n">
         <v>0</v>
@@ -24776,7 +24776,7 @@
         <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="AB174" t="n">
         <v>5</v>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -26012,10 +26012,10 @@
         <v>452872.05</v>
       </c>
       <c r="S183" t="n">
-        <v>350000</v>
+        <v>452872.05</v>
       </c>
       <c r="T183" t="n">
-        <v>350000</v>
+        <v>452872.05</v>
       </c>
       <c r="U183" t="n">
         <v>452872.05</v>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -26271,7 +26271,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>7122000</v>
+        <v>7108000</v>
       </c>
       <c r="M185" t="n">
         <v>0</v>
@@ -26280,7 +26280,7 @@
         <v>371000</v>
       </c>
       <c r="O185" t="n">
-        <v>6289600</v>
+        <v>6275600</v>
       </c>
       <c r="P185" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -26420,7 +26420,7 @@
         <v>2800000</v>
       </c>
       <c r="O186" t="n">
-        <v>24181560.43</v>
+        <v>24197313.15</v>
       </c>
       <c r="P186" t="n">
         <v>1885306.26</v>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -29652,10 +29652,10 @@
         <v>200000</v>
       </c>
       <c r="S209" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="T209" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="U209" t="n">
         <v>200000</v>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -29911,7 +29911,7 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>34068633.7</v>
+        <v>34668633.7</v>
       </c>
       <c r="M211" t="n">
         <v>0</v>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -30471,7 +30471,7 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>138273116.26</v>
+        <v>139713847.28</v>
       </c>
       <c r="M215" t="n">
         <v>0</v>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -30891,7 +30891,7 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>71986213.70999999</v>
+        <v>74449783.70999999</v>
       </c>
       <c r="M218" t="n">
         <v>0</v>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -31040,7 +31040,7 @@
         <v>0</v>
       </c>
       <c r="O219" t="n">
-        <v>54471982.83</v>
+        <v>54651982.83</v>
       </c>
       <c r="P219" t="n">
         <v>50438263.91</v>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>
@@ -32023,7 +32023,7 @@
         <v>35122742.46</v>
       </c>
       <c r="P226" t="n">
-        <v>6884747.48</v>
+        <v>6952882.48</v>
       </c>
       <c r="Q226" t="n">
         <v>0</v>
@@ -32032,13 +32032,13 @@
         <v>49535258.91</v>
       </c>
       <c r="S226" t="n">
-        <v>39254641.52</v>
+        <v>39557476.52</v>
       </c>
       <c r="T226" t="n">
-        <v>40867405.68</v>
+        <v>41170240.68</v>
       </c>
       <c r="U226" t="n">
-        <v>42650511.43</v>
+        <v>42582376.43</v>
       </c>
       <c r="V226" t="n">
         <v>1612764.16</v>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>03/09/2026 10:43:09</t>
+          <t>04/09/2026 10:30:59</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4856311.31</v>
+        <v>5033812.52</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1789,7 +1789,7 @@
         <v>3096601.89</v>
       </c>
       <c r="R10" t="n">
-        <v>20244601.43</v>
+        <v>20257146.43</v>
       </c>
       <c r="S10" t="n">
         <v>9705526.23</v>
@@ -1798,7 +1798,7 @@
         <v>11248777.65</v>
       </c>
       <c r="U10" t="n">
-        <v>11855687.01</v>
+        <v>11868232.01</v>
       </c>
       <c r="V10" t="n">
         <v>1543251.42</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3503838.53</v>
+        <v>3509598.53</v>
       </c>
       <c r="P20" t="n">
         <v>4312664.33</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
         <v>261000</v>
       </c>
       <c r="O30" t="n">
-        <v>1142642.78</v>
+        <v>1145867.82</v>
       </c>
       <c r="P30" t="n">
         <v>653221.75</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>9491342.720000001</v>
+        <v>9491342.73</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>725144</v>
       </c>
       <c r="O32" t="n">
-        <v>9407082.59</v>
+        <v>9490556.18</v>
       </c>
       <c r="P32" t="n">
         <v>6111721.43</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -6552,10 +6552,10 @@
         <v>187832.03</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>68800</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>68800</v>
       </c>
       <c r="U44" t="n">
         <v>90839.46000000001</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -6832,10 +6832,10 @@
         <v>31629021.26</v>
       </c>
       <c r="S46" t="n">
-        <v>5894529.44</v>
+        <v>5945729.44</v>
       </c>
       <c r="T46" t="n">
-        <v>6394979</v>
+        <v>6446179</v>
       </c>
       <c r="U46" t="n">
         <v>14251491.61</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>146026.49</v>
+        <v>175738.68</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>7096288.58</v>
+        <v>7363410.03</v>
       </c>
       <c r="P52" t="n">
         <v>4589956.52</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -12992,10 +12992,10 @@
         <v>190000</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="T90" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="U90" t="n">
         <v>190000</v>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -21651,7 +21651,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1455137.56</v>
+        <v>1456637.56</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -23340,7 +23340,7 @@
         <v>211572</v>
       </c>
       <c r="O164" t="n">
-        <v>1655046.36</v>
+        <v>1769046.36</v>
       </c>
       <c r="P164" t="n">
         <v>2709234.52</v>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -26420,7 +26420,7 @@
         <v>2800000</v>
       </c>
       <c r="O186" t="n">
-        <v>24197313.15</v>
+        <v>24420778.67</v>
       </c>
       <c r="P186" t="n">
         <v>1885306.26</v>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -26980,7 +26980,7 @@
         <v>0</v>
       </c>
       <c r="O190" t="n">
-        <v>1520782.37</v>
+        <v>1540908.15</v>
       </c>
       <c r="P190" t="n">
         <v>2316998.65</v>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -28949,7 +28949,7 @@
         <v>39738</v>
       </c>
       <c r="R204" t="n">
-        <v>44500</v>
+        <v>46600</v>
       </c>
       <c r="S204" t="n">
         <v>32500</v>
@@ -28958,7 +28958,7 @@
         <v>33100</v>
       </c>
       <c r="U204" t="n">
-        <v>33100</v>
+        <v>35200</v>
       </c>
       <c r="V204" t="n">
         <v>600</v>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -30471,7 +30471,7 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>139713847.28</v>
+        <v>141029238.38</v>
       </c>
       <c r="M215" t="n">
         <v>0</v>
@@ -30480,7 +30480,7 @@
         <v>0</v>
       </c>
       <c r="O215" t="n">
-        <v>126414514.22</v>
+        <v>135617990.41</v>
       </c>
       <c r="P215" t="n">
         <v>49808521.04</v>
@@ -30489,7 +30489,7 @@
         <v>5086650.13</v>
       </c>
       <c r="R215" t="n">
-        <v>214390827.25</v>
+        <v>215048522.8</v>
       </c>
       <c r="S215" t="n">
         <v>163819531.01</v>
@@ -30498,7 +30498,7 @@
         <v>169486907.25</v>
       </c>
       <c r="U215" t="n">
-        <v>164582306.21</v>
+        <v>165240001.76</v>
       </c>
       <c r="V215" t="n">
         <v>5667376.24</v>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -30891,7 +30891,7 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>74449783.70999999</v>
+        <v>76878033.70999999</v>
       </c>
       <c r="M218" t="n">
         <v>0</v>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -31311,7 +31311,7 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>784000</v>
+        <v>907561.39</v>
       </c>
       <c r="M221" t="n">
         <v>0</v>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>
@@ -32011,7 +32011,7 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>36382287.88</v>
+        <v>36646414.73</v>
       </c>
       <c r="M226" t="n">
         <v>0</v>
@@ -32020,7 +32020,7 @@
         <v>0</v>
       </c>
       <c r="O226" t="n">
-        <v>35122742.46</v>
+        <v>35362303.78</v>
       </c>
       <c r="P226" t="n">
         <v>6952882.48</v>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>04/09/2026 10:30:59</t>
+          <t>05/09/2026 09:46:22</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
         <v>197487</v>
       </c>
       <c r="O11" t="n">
-        <v>163590.91</v>
+        <v>165003.57</v>
       </c>
       <c r="P11" t="n">
         <v>200450</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
         <v>93886</v>
       </c>
       <c r="O46" t="n">
-        <v>2696862.84</v>
+        <v>2716076.57</v>
       </c>
       <c r="P46" t="n">
         <v>17377529.65</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -26980,7 +26980,7 @@
         <v>0</v>
       </c>
       <c r="O190" t="n">
-        <v>1540908.15</v>
+        <v>1573472.63</v>
       </c>
       <c r="P190" t="n">
         <v>2316998.65</v>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -28520,7 +28520,7 @@
         <v>0</v>
       </c>
       <c r="O201" t="n">
-        <v>273660.67</v>
+        <v>318270.87</v>
       </c>
       <c r="P201" t="n">
         <v>2957320.94</v>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -31040,7 +31040,7 @@
         <v>0</v>
       </c>
       <c r="O219" t="n">
-        <v>54651982.83</v>
+        <v>54741982.83</v>
       </c>
       <c r="P219" t="n">
         <v>50438263.91</v>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>05/09/2026 09:46:22</t>
+          <t>06/09/2026 09:57:33</t>
         </is>
       </c>
     </row>
